--- a/templates/source_onboarding_template.xlsx
+++ b/templates/source_onboarding_template.xlsx
@@ -434,7 +434,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Q2"/>
+  <dimension ref="A1:R2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
@@ -454,6 +454,7 @@
     <col width="21" customWidth="1" min="15" max="15"/>
     <col width="20" customWidth="1" min="16" max="16"/>
     <col width="27" customWidth="1" min="17" max="17"/>
+    <col width="27" customWidth="1" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -542,6 +543,11 @@
           <t>gate_mr_report_blocking</t>
         </is>
       </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>expected_table_strategy</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -604,6 +610,11 @@
       </c>
       <c r="Q2" t="b">
         <v>0</v>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>view</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/templates/source_onboarding_template.xlsx
+++ b/templates/source_onboarding_template.xlsx
@@ -1279,7 +1279,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:H2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="20" customWidth="1" min="1" max="1"/>
@@ -1289,6 +1289,7 @@
     <col width="18" customWidth="1" min="5" max="5"/>
     <col width="14" customWidth="1" min="6" max="6"/>
     <col width="25" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1327,6 +1328,11 @@
           <t>expected_sql_override</t>
         </is>
       </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>cardinality</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1352,6 +1358,7 @@
       </c>
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1364,7 +1371,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1377,6 +1384,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1430,6 +1442,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1466,6 +1503,13 @@
           <t>TODO(mapping-pending): EXAMPLE_INPUT layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1478,7 +1522,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1491,6 +1535,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1544,6 +1593,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1580,6 +1654,13 @@
           <t>TODO(mapping-pending): EXAMPLE_OUTPUT layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1592,7 +1673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1605,6 +1686,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1658,6 +1744,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1694,6 +1805,13 @@
           <t>TODO(mapping-pending): EXAMPLE_MR_OUTPUT_BATCH_HEADER layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1706,7 +1824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J2"/>
+  <dimension ref="A1:O2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1719,6 +1837,11 @@
     <col width="18" customWidth="1" min="8" max="8"/>
     <col width="16" customWidth="1" min="9" max="9"/>
     <col width="15" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="24" customWidth="1" min="12" max="12"/>
+    <col width="25" customWidth="1" min="13" max="13"/>
+    <col width="28" customWidth="1" min="14" max="14"/>
+    <col width="33" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1772,6 +1895,31 @@
           <t>Description</t>
         </is>
       </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Order</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Column</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation Predicate</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Reconciliation SQL Expression</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1808,6 +1956,13 @@
           <t>TODO(mapping-pending): EXAMPLE_MR_OUTPUT_DETAIL layout not yet authored. Replace this row with real fields before onboarding.</t>
         </is>
       </c>
+      <c r="K2" t="b">
+        <v>0</v>
+      </c>
+      <c r="L2" t="inlineStr"/>
+      <c r="M2" t="inlineStr"/>
+      <c r="N2" t="inlineStr"/>
+      <c r="O2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
